--- a/00baseDatos/redestemproalesidactualizadomatricescuantitativass/ID-ACTUALIZADO-total de redes.xlsx
+++ b/00baseDatos/redestemproalesidactualizadomatricescuantitativass/ID-ACTUALIZADO-total de redes.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="187">
   <si>
     <t xml:space="preserve">ID - Base de datos</t>
   </si>
@@ -229,6 +229,9 @@
     <t xml:space="preserve">Denmark</t>
   </si>
   <si>
+    <t xml:space="preserve">ABEJ -IA</t>
+  </si>
+  <si>
     <t xml:space="preserve">019_Inouye_1988</t>
   </si>
   <si>
@@ -236,6 +239,9 @@
   </si>
   <si>
     <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ai – BEJA</t>
   </si>
   <si>
     <t xml:space="preserve">020_Kevan et al _1970</t>
@@ -595,7 +601,6 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -616,7 +621,6 @@
       <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -963,7 +967,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I71"/>
-  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="49.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.27"/>
@@ -973,7 +977,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="27.64"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1182,7 +1186,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>36</v>
       </c>
@@ -1317,7 +1321,7 @@
         <v>-71.3</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
         <v>58</v>
       </c>
@@ -1357,7 +1361,7 @@
         <v>-6.55</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
         <v>63</v>
       </c>
@@ -1396,19 +1400,22 @@
       <c r="F20" s="15" t="n">
         <v>9.973652</v>
       </c>
+      <c r="I20" s="0" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>-36.45</v>
@@ -1416,13 +1423,16 @@
       <c r="F21" s="10" t="n">
         <v>148.27</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>9</v>
@@ -1439,16 +1449,16 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>35.33</v>
@@ -1459,16 +1469,16 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>-34.17</v>
@@ -1479,16 +1489,16 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>78</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>-33</v>
@@ -1499,10 +1509,10 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>42</v>
@@ -1515,10 +1525,10 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>42</v>
@@ -1535,32 +1545,32 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E29" s="16" t="n">
         <v>-42.95</v>
@@ -1571,16 +1581,16 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>90</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>-43.03</v>
@@ -1591,16 +1601,16 @@
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>-43.1</v>
@@ -1611,16 +1621,16 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>8.93</v>
@@ -1629,18 +1639,18 @@
         <v>-67.42</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>97</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>5.58</v>
@@ -1651,10 +1661,10 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>42</v>
@@ -1671,10 +1681,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>42</v>
@@ -1691,10 +1701,10 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>9</v>
@@ -1709,18 +1719,18 @@
         <v>-73.58</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>17.92</v>
@@ -1731,16 +1741,16 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E38" s="15" t="n">
         <v>39.46667</v>
@@ -1749,12 +1759,12 @@
         <v>-31.22722</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>9</v>
@@ -1771,10 +1781,10 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>9</v>
@@ -1791,10 +1801,10 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>9</v>
@@ -1803,18 +1813,18 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>18.35</v>
@@ -1823,18 +1833,18 @@
         <v>-77.65</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B43" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>120</v>
-      </c>
       <c r="D43" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>15.52</v>
@@ -1845,26 +1855,26 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>9</v>
@@ -1881,14 +1891,14 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>28.38</v>
@@ -1899,10 +1909,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C47" s="26" t="s">
         <v>9</v>
@@ -1919,10 +1929,10 @@
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>9</v>
@@ -1939,10 +1949,10 @@
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>9</v>
@@ -1953,10 +1963,10 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>9</v>
@@ -1973,32 +1983,32 @@
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C51" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>33.4</v>
@@ -2009,16 +2019,16 @@
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C53" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>35.03</v>
@@ -2029,16 +2039,16 @@
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C54" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>35.65</v>
@@ -2049,16 +2059,16 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C55" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E55" s="10" t="n">
         <v>35.58</v>
@@ -2069,16 +2079,16 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C56" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>35.17</v>
@@ -2089,10 +2099,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>42</v>
@@ -2109,16 +2119,16 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C58" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>-8.51</v>
@@ -2129,10 +2139,10 @@
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C59" s="19" t="s">
         <v>42</v>
@@ -2141,24 +2151,24 @@
         <v>43</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C60" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E60" s="16" t="n">
         <v>-4.67</v>
@@ -2169,10 +2179,10 @@
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>9</v>
@@ -2189,16 +2199,16 @@
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C62" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E62" s="16" t="n">
         <v>-37.84201</v>
@@ -2207,12 +2217,12 @@
         <v>-58.358571</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C63" s="19" t="s">
         <v>42</v>
@@ -2229,16 +2239,16 @@
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>-25.4</v>
@@ -2249,10 +2259,10 @@
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C65" s="19" t="s">
         <v>42</v>
@@ -2269,10 +2279,10 @@
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C66" s="19" t="s">
         <v>42</v>
@@ -2289,16 +2299,16 @@
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E67" s="16" t="n">
         <v>-12.7</v>
@@ -2307,18 +2317,18 @@
         <v>-39.7667</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C68" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E68" s="29" t="n">
         <v>-19.936</v>
@@ -2329,32 +2339,32 @@
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E69" s="22"/>
       <c r="F69" s="22"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C70" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E70" s="10" t="n">
         <v>-32.53</v>
@@ -2365,10 +2375,10 @@
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C71" s="19" t="s">
         <v>42</v>
